--- a/ig/DM-MARS-2026/CodeSystem-tre-r382-modalite-act-de-soin-amm.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-tre-r382-modalite-act-de-soin-amm.xlsx
@@ -397,7 +397,7 @@
     <t>MO047</t>
   </si>
   <si>
-    <t>AMP CLI -  Prélèvement d'ovocytes en vue d'une AMP</t>
+    <t>AMP CLI - Prélèvement d'ovocytes en vue d'une AMP</t>
   </si>
   <si>
     <t>MO048</t>
@@ -409,7 +409,7 @@
     <t>MO049</t>
   </si>
   <si>
-    <t xml:space="preserve">AMP CLI -  Prélèvement de spermatozoïdes </t>
+    <t>AMP CLI - Prélèvement de spermatozoïdes</t>
   </si>
   <si>
     <t>MO050</t>
@@ -439,7 +439,7 @@
     <t>MO059</t>
   </si>
   <si>
-    <t>AMP BIO -  Conservation des embryons en vue de leur accueil et mise en œuvre de celui-ci</t>
+    <t>AMP BIO - Conservation des embryons en vue de leur accueil et mise en œuvre de celui-ci</t>
   </si>
   <si>
     <t>MO060</t>
@@ -457,13 +457,13 @@
     <t>MO073</t>
   </si>
   <si>
-    <t xml:space="preserve">AMP CLI - Mise en œuvre de l'Accueil des embryons </t>
+    <t>AMP CLI - Mise en œuvre de l'Accueil des embryons</t>
   </si>
   <si>
     <t>MO074</t>
   </si>
   <si>
-    <t xml:space="preserve">AMP BIO - Conservation des embryons en vue d'un projet parental </t>
+    <t>AMP BIO - Conservation des embryons en vue d'un projet parental</t>
   </si>
   <si>
     <t>MO075</t>
